--- a/fundraiser_forms/007_veggie_fundraising_participation_form--fundraiser_forms.xlsx
+++ b/fundraiser_forms/007_veggie_fundraising_participation_form--fundraiser_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1146,8 +1146,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="41" customWidth="1" min="2" max="2"/>
-    <col width="41" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1175,12 +1175,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'delivery'}</t>
+          <t>delivery</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Delivery'}</t>
+          <t>Delivery</t>
         </is>
       </c>
     </row>
@@ -1192,12 +1192,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'pickup'}</t>
+          <t>pickup</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Pickup'}</t>
+          <t>Pickup</t>
         </is>
       </c>
     </row>
@@ -1209,12 +1209,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1226,12 +1226,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1243,12 +1243,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'maybe'}</t>
+          <t>maybe</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Maybe'}</t>
+          <t>Maybe</t>
         </is>
       </c>
     </row>
@@ -1260,12 +1260,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1277,12 +1277,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'local_pickup'}</t>
+          <t>local_pickup</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Local Pickup'}</t>
+          <t>Local Pickup</t>
         </is>
       </c>
     </row>
@@ -1294,12 +1294,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'local_delivery'}</t>
+          <t>local_delivery</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Local Delivery'}</t>
+          <t>Local Delivery</t>
         </is>
       </c>
     </row>
@@ -1311,12 +1311,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1328,12 +1328,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'self_pickup'}</t>
+          <t>self_pickup</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Self Pickup'}</t>
+          <t>Self Pickup</t>
         </is>
       </c>
     </row>
@@ -1345,12 +1345,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'drop-off_at_a_local_office'}</t>
+          <t>drop-off_at_a_local_office</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Drop-off at a local office'}</t>
+          <t>Drop-off at a local office</t>
         </is>
       </c>
     </row>
@@ -1362,12 +1362,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'delivery_to_home'}</t>
+          <t>delivery_to_home</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Delivery to home'}</t>
+          <t>Delivery to home</t>
         </is>
       </c>
     </row>
@@ -1379,12 +1379,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1396,12 +1396,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1430,12 +1430,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1447,12 +1447,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1464,12 +1464,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1481,12 +1481,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1498,12 +1498,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1515,12 +1515,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
